--- a/銀行明細集計.xlsx
+++ b/銀行明細集計.xlsx
@@ -8,8 +8,9 @@
   <sheets>
     <sheet name="設定" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="統合決済履歴" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="月別集計" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="トータル集計" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="月別_2026年8月" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="月別_2026年9月" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="トータル集計" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'統合決済履歴'!$A$1:$K$198</definedName>
@@ -10865,7 +10866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E147"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -10875,7 +10876,7 @@
     <row r="1" ht="16.8" customHeight="1">
       <c r="A1" s="28" t="inlineStr">
         <is>
-          <t>2026年9月</t>
+          <t>2026年8月</t>
         </is>
       </c>
     </row>
@@ -10921,15 +10922,15 @@
         </is>
       </c>
       <c r="B5" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C5" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D5" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E5" s="32">
@@ -10944,15 +10945,15 @@
         </is>
       </c>
       <c r="B6" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C6" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D6" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E6" s="32">
@@ -10967,15 +10968,15 @@
         </is>
       </c>
       <c r="B7" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C7" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D7" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E7" s="32">
@@ -10990,15 +10991,15 @@
         </is>
       </c>
       <c r="B8" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C8" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D8" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E8" s="32">
@@ -11013,15 +11014,15 @@
         </is>
       </c>
       <c r="B9" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C9" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D9" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E9" s="32">
@@ -11036,15 +11037,15 @@
         </is>
       </c>
       <c r="B10" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C10" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D10" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E10" s="32">
@@ -11059,15 +11060,15 @@
         </is>
       </c>
       <c r="B11" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C11" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D11" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E11" s="32">
@@ -11082,15 +11083,15 @@
         </is>
       </c>
       <c r="B12" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C12" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D12" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E12" s="32">
@@ -11105,15 +11106,15 @@
         </is>
       </c>
       <c r="B13" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C13" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D13" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E13" s="32">
@@ -11128,15 +11129,15 @@
         </is>
       </c>
       <c r="B14" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C14" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D14" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E14" s="32">
@@ -11209,15 +11210,15 @@
         </is>
       </c>
       <c r="B19" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C19" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D19" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E19" s="32">
@@ -11232,15 +11233,15 @@
         </is>
       </c>
       <c r="B20" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C20" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D20" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E20" s="32">
@@ -11255,15 +11256,15 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C21" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D21" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E21" s="32">
@@ -11278,15 +11279,15 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C22" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D22" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E22" s="32">
@@ -11301,15 +11302,15 @@
         </is>
       </c>
       <c r="B23" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C23" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D23" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E23" s="32">
@@ -11324,15 +11325,15 @@
         </is>
       </c>
       <c r="B24" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C24" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D24" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E24" s="32">
@@ -11347,15 +11348,15 @@
         </is>
       </c>
       <c r="B25" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C25" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D25" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E25" s="32">
@@ -11370,15 +11371,15 @@
         </is>
       </c>
       <c r="B26" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C26" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D26" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E26" s="32">
@@ -11393,15 +11394,15 @@
         </is>
       </c>
       <c r="B27" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C27" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D27" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E27" s="32">
@@ -11416,15 +11417,15 @@
         </is>
       </c>
       <c r="B28" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C28" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D28" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E28" s="32">
@@ -11497,15 +11498,15 @@
         </is>
       </c>
       <c r="B33" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C33" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D33" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E33" s="32">
@@ -11520,15 +11521,15 @@
         </is>
       </c>
       <c r="B34" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C34" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D34" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E34" s="32">
@@ -11543,15 +11544,15 @@
         </is>
       </c>
       <c r="B35" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C35" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D35" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E35" s="32">
@@ -11566,15 +11567,15 @@
         </is>
       </c>
       <c r="B36" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C36" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D36" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E36" s="32">
@@ -11589,15 +11590,15 @@
         </is>
       </c>
       <c r="B37" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C37" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D37" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E37" s="32">
@@ -11612,15 +11613,15 @@
         </is>
       </c>
       <c r="B38" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C38" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D38" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E38" s="32">
@@ -11635,15 +11636,15 @@
         </is>
       </c>
       <c r="B39" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C39" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D39" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E39" s="32">
@@ -11658,15 +11659,15 @@
         </is>
       </c>
       <c r="B40" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C40" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D40" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E40" s="32">
@@ -11681,15 +11682,15 @@
         </is>
       </c>
       <c r="B41" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C41" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D41" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E41" s="32">
@@ -11704,15 +11705,15 @@
         </is>
       </c>
       <c r="B42" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C42" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D42" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E42" s="32">
@@ -11785,15 +11786,15 @@
         </is>
       </c>
       <c r="B47" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C47" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D47" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E47" s="32">
@@ -11808,15 +11809,15 @@
         </is>
       </c>
       <c r="B48" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C48" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D48" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E48" s="32">
@@ -11831,15 +11832,15 @@
         </is>
       </c>
       <c r="B49" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C49" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D49" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E49" s="32">
@@ -11854,15 +11855,15 @@
         </is>
       </c>
       <c r="B50" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C50" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D50" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E50" s="32">
@@ -11877,15 +11878,15 @@
         </is>
       </c>
       <c r="B51" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C51" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D51" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E51" s="32">
@@ -11900,15 +11901,15 @@
         </is>
       </c>
       <c r="B52" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C52" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D52" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E52" s="32">
@@ -11923,15 +11924,15 @@
         </is>
       </c>
       <c r="B53" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C53" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D53" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E53" s="32">
@@ -11946,15 +11947,15 @@
         </is>
       </c>
       <c r="B54" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C54" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D54" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E54" s="32">
@@ -11969,15 +11970,15 @@
         </is>
       </c>
       <c r="B55" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C55" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D55" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E55" s="32">
@@ -11992,15 +11993,15 @@
         </is>
       </c>
       <c r="B56" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C56" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D56" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E56" s="32">
@@ -12073,15 +12074,15 @@
         </is>
       </c>
       <c r="B61" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C61" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D61" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E61" s="32">
@@ -12096,15 +12097,15 @@
         </is>
       </c>
       <c r="B62" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C62" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D62" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E62" s="32">
@@ -12119,15 +12120,15 @@
         </is>
       </c>
       <c r="B63" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C63" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D63" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E63" s="32">
@@ -12142,15 +12143,15 @@
         </is>
       </c>
       <c r="B64" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C64" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D64" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E64" s="32">
@@ -12165,15 +12166,15 @@
         </is>
       </c>
       <c r="B65" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C65" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D65" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E65" s="32">
@@ -12188,15 +12189,15 @@
         </is>
       </c>
       <c r="B66" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C66" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D66" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E66" s="32">
@@ -12211,15 +12212,15 @@
         </is>
       </c>
       <c r="B67" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C67" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D67" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E67" s="32">
@@ -12234,15 +12235,15 @@
         </is>
       </c>
       <c r="B68" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C68" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D68" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E68" s="32">
@@ -12257,15 +12258,15 @@
         </is>
       </c>
       <c r="B69" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C69" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D69" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E69" s="32">
@@ -12280,15 +12281,15 @@
         </is>
       </c>
       <c r="B70" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="C70" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="D70" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
         <v/>
       </c>
       <c r="E70" s="32">
@@ -12319,1455 +12320,7 @@
         <v/>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="28" t="inlineStr">
-        <is>
-          <t>2026年8月</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t>■ 聖也</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>カテゴリ</t>
-        </is>
-      </c>
-      <c r="B77" s="29" t="inlineStr">
-        <is>
-          <t>GBP 合計</t>
-        </is>
-      </c>
-      <c r="C77" s="29" t="inlineStr">
-        <is>
-          <t>EUR 合計</t>
-        </is>
-      </c>
-      <c r="D77" s="29" t="inlineStr">
-        <is>
-          <t>JPY 合計</t>
-        </is>
-      </c>
-      <c r="E77" s="29" t="inlineStr">
-        <is>
-          <t>JPY換算合計</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Bills</t>
-        </is>
-      </c>
-      <c r="B78" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C78" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D78" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E78" s="32">
-        <f>B78*設定!$B$3+C78*設定!$B$4+D78</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="30" t="inlineStr">
-        <is>
-          <t>Eating out</t>
-        </is>
-      </c>
-      <c r="B79" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C79" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D79" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E79" s="32">
-        <f>B79*設定!$B$3+C79*設定!$B$4+D79</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="30" t="inlineStr">
-        <is>
-          <t>Entertainment</t>
-        </is>
-      </c>
-      <c r="B80" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C80" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D80" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E80" s="32">
-        <f>B80*設定!$B$3+C80*設定!$B$4+D80</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="30" t="inlineStr">
-        <is>
-          <t>Family</t>
-        </is>
-      </c>
-      <c r="B81" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C81" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D81" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E81" s="32">
-        <f>B81*設定!$B$3+C81*設定!$B$4+D81</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="30" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="B82" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C82" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D82" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E82" s="32">
-        <f>B82*設定!$B$3+C82*設定!$B$4+D82</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="30" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="B83" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C83" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D83" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E83" s="32">
-        <f>B83*設定!$B$3+C83*設定!$B$4+D83</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="30" t="inlineStr">
-        <is>
-          <t>Money added</t>
-        </is>
-      </c>
-      <c r="B84" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C84" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D84" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E84" s="32">
-        <f>B84*設定!$B$3+C84*設定!$B$4+D84</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="30" t="inlineStr">
-        <is>
-          <t>Personal care</t>
-        </is>
-      </c>
-      <c r="B85" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C85" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D85" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E85" s="32">
-        <f>B85*設定!$B$3+C85*設定!$B$4+D85</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="30" t="inlineStr">
-        <is>
-          <t>Shopping</t>
-        </is>
-      </c>
-      <c r="B86" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C86" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D86" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E86" s="32">
-        <f>B86*設定!$B$3+C86*設定!$B$4+D86</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="30" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="B87" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C87" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D87" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E87" s="32">
-        <f>B87*設定!$B$3+C87*設定!$B$4+D87</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="36" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="B88" s="37">
-        <f>SUM(B78:B87)</f>
-        <v/>
-      </c>
-      <c r="C88" s="37">
-        <f>SUM(C78:C87)</f>
-        <v/>
-      </c>
-      <c r="D88" s="37">
-        <f>SUM(D78:D87)</f>
-        <v/>
-      </c>
-      <c r="E88" s="38">
-        <f>SUM(E78:E87)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="1" t="inlineStr">
-        <is>
-          <t>■ 愛弓</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>カテゴリ</t>
-        </is>
-      </c>
-      <c r="B91" s="29" t="inlineStr">
-        <is>
-          <t>GBP 合計</t>
-        </is>
-      </c>
-      <c r="C91" s="29" t="inlineStr">
-        <is>
-          <t>EUR 合計</t>
-        </is>
-      </c>
-      <c r="D91" s="29" t="inlineStr">
-        <is>
-          <t>JPY 合計</t>
-        </is>
-      </c>
-      <c r="E91" s="29" t="inlineStr">
-        <is>
-          <t>JPY換算合計</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="30" t="inlineStr">
-        <is>
-          <t>Bills</t>
-        </is>
-      </c>
-      <c r="B92" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C92" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D92" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E92" s="32">
-        <f>B92*設定!$B$3+C92*設定!$B$4+D92</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="30" t="inlineStr">
-        <is>
-          <t>Eating out</t>
-        </is>
-      </c>
-      <c r="B93" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C93" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D93" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E93" s="32">
-        <f>B93*設定!$B$3+C93*設定!$B$4+D93</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="30" t="inlineStr">
-        <is>
-          <t>Entertainment</t>
-        </is>
-      </c>
-      <c r="B94" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C94" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D94" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E94" s="32">
-        <f>B94*設定!$B$3+C94*設定!$B$4+D94</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="30" t="inlineStr">
-        <is>
-          <t>Family</t>
-        </is>
-      </c>
-      <c r="B95" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C95" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D95" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E95" s="32">
-        <f>B95*設定!$B$3+C95*設定!$B$4+D95</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="30" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="B96" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C96" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D96" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E96" s="32">
-        <f>B96*設定!$B$3+C96*設定!$B$4+D96</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="30" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="B97" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C97" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D97" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E97" s="32">
-        <f>B97*設定!$B$3+C97*設定!$B$4+D97</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="30" t="inlineStr">
-        <is>
-          <t>Money added</t>
-        </is>
-      </c>
-      <c r="B98" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C98" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D98" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E98" s="32">
-        <f>B98*設定!$B$3+C98*設定!$B$4+D98</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="30" t="inlineStr">
-        <is>
-          <t>Personal care</t>
-        </is>
-      </c>
-      <c r="B99" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C99" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D99" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E99" s="32">
-        <f>B99*設定!$B$3+C99*設定!$B$4+D99</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="30" t="inlineStr">
-        <is>
-          <t>Shopping</t>
-        </is>
-      </c>
-      <c r="B100" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C100" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D100" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E100" s="32">
-        <f>B100*設定!$B$3+C100*設定!$B$4+D100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="30" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="B101" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C101" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D101" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E101" s="32">
-        <f>B101*設定!$B$3+C101*設定!$B$4+D101</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="36" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="B102" s="37">
-        <f>SUM(B92:B101)</f>
-        <v/>
-      </c>
-      <c r="C102" s="37">
-        <f>SUM(C92:C101)</f>
-        <v/>
-      </c>
-      <c r="D102" s="37">
-        <f>SUM(D92:D101)</f>
-        <v/>
-      </c>
-      <c r="E102" s="38">
-        <f>SUM(E92:E101)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="1" t="inlineStr">
-        <is>
-          <t>■ 共通</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>カテゴリ</t>
-        </is>
-      </c>
-      <c r="B105" s="29" t="inlineStr">
-        <is>
-          <t>GBP 合計</t>
-        </is>
-      </c>
-      <c r="C105" s="29" t="inlineStr">
-        <is>
-          <t>EUR 合計</t>
-        </is>
-      </c>
-      <c r="D105" s="29" t="inlineStr">
-        <is>
-          <t>JPY 合計</t>
-        </is>
-      </c>
-      <c r="E105" s="29" t="inlineStr">
-        <is>
-          <t>JPY換算合計</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="30" t="inlineStr">
-        <is>
-          <t>Bills</t>
-        </is>
-      </c>
-      <c r="B106" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C106" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D106" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E106" s="32">
-        <f>B106*設定!$B$3+C106*設定!$B$4+D106</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="30" t="inlineStr">
-        <is>
-          <t>Eating out</t>
-        </is>
-      </c>
-      <c r="B107" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C107" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D107" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E107" s="32">
-        <f>B107*設定!$B$3+C107*設定!$B$4+D107</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="30" t="inlineStr">
-        <is>
-          <t>Entertainment</t>
-        </is>
-      </c>
-      <c r="B108" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C108" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D108" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E108" s="32">
-        <f>B108*設定!$B$3+C108*設定!$B$4+D108</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="30" t="inlineStr">
-        <is>
-          <t>Family</t>
-        </is>
-      </c>
-      <c r="B109" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C109" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D109" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E109" s="32">
-        <f>B109*設定!$B$3+C109*設定!$B$4+D109</f>
-        <v/>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="30" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="B110" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C110" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D110" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E110" s="32">
-        <f>B110*設定!$B$3+C110*設定!$B$4+D110</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="30" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="B111" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C111" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D111" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E111" s="32">
-        <f>B111*設定!$B$3+C111*設定!$B$4+D111</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="30" t="inlineStr">
-        <is>
-          <t>Money added</t>
-        </is>
-      </c>
-      <c r="B112" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C112" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D112" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E112" s="32">
-        <f>B112*設定!$B$3+C112*設定!$B$4+D112</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="30" t="inlineStr">
-        <is>
-          <t>Personal care</t>
-        </is>
-      </c>
-      <c r="B113" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C113" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D113" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E113" s="32">
-        <f>B113*設定!$B$3+C113*設定!$B$4+D113</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="30" t="inlineStr">
-        <is>
-          <t>Shopping</t>
-        </is>
-      </c>
-      <c r="B114" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C114" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D114" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E114" s="32">
-        <f>B114*設定!$B$3+C114*設定!$B$4+D114</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="30" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="B115" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C115" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D115" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E115" s="32">
-        <f>B115*設定!$B$3+C115*設定!$B$4+D115</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="36" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="B116" s="37">
-        <f>SUM(B106:B115)</f>
-        <v/>
-      </c>
-      <c r="C116" s="37">
-        <f>SUM(C106:C115)</f>
-        <v/>
-      </c>
-      <c r="D116" s="37">
-        <f>SUM(D106:D115)</f>
-        <v/>
-      </c>
-      <c r="E116" s="38">
-        <f>SUM(E106:E115)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="1" t="inlineStr">
-        <is>
-          <t>■ 合計（聖也＋愛弓＋共通、除外を除く）</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>カテゴリ</t>
-        </is>
-      </c>
-      <c r="B119" s="29" t="inlineStr">
-        <is>
-          <t>GBP 合計</t>
-        </is>
-      </c>
-      <c r="C119" s="29" t="inlineStr">
-        <is>
-          <t>EUR 合計</t>
-        </is>
-      </c>
-      <c r="D119" s="29" t="inlineStr">
-        <is>
-          <t>JPY 合計</t>
-        </is>
-      </c>
-      <c r="E119" s="29" t="inlineStr">
-        <is>
-          <t>JPY換算合計</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="30" t="inlineStr">
-        <is>
-          <t>Bills</t>
-        </is>
-      </c>
-      <c r="B120" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C120" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D120" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E120" s="32">
-        <f>B120*設定!$B$3+C120*設定!$B$4+D120</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="30" t="inlineStr">
-        <is>
-          <t>Eating out</t>
-        </is>
-      </c>
-      <c r="B121" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C121" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D121" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E121" s="32">
-        <f>B121*設定!$B$3+C121*設定!$B$4+D121</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="30" t="inlineStr">
-        <is>
-          <t>Entertainment</t>
-        </is>
-      </c>
-      <c r="B122" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C122" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D122" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E122" s="32">
-        <f>B122*設定!$B$3+C122*設定!$B$4+D122</f>
-        <v/>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="30" t="inlineStr">
-        <is>
-          <t>Family</t>
-        </is>
-      </c>
-      <c r="B123" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C123" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D123" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E123" s="32">
-        <f>B123*設定!$B$3+C123*設定!$B$4+D123</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="30" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="B124" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C124" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D124" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E124" s="32">
-        <f>B124*設定!$B$3+C124*設定!$B$4+D124</f>
-        <v/>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="30" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="B125" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C125" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D125" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E125" s="32">
-        <f>B125*設定!$B$3+C125*設定!$B$4+D125</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="30" t="inlineStr">
-        <is>
-          <t>Money added</t>
-        </is>
-      </c>
-      <c r="B126" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C126" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D126" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E126" s="32">
-        <f>B126*設定!$B$3+C126*設定!$B$4+D126</f>
-        <v/>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="30" t="inlineStr">
-        <is>
-          <t>Personal care</t>
-        </is>
-      </c>
-      <c r="B127" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C127" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D127" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E127" s="32">
-        <f>B127*設定!$B$3+C127*設定!$B$4+D127</f>
-        <v/>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="30" t="inlineStr">
-        <is>
-          <t>Shopping</t>
-        </is>
-      </c>
-      <c r="B128" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C128" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D128" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E128" s="32">
-        <f>B128*設定!$B$3+C128*設定!$B$4+D128</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="30" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="B129" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C129" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D129" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E129" s="32">
-        <f>B129*設定!$B$3+C129*設定!$B$4+D129</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="36" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="B130" s="37">
-        <f>SUM(B120:B129)</f>
-        <v/>
-      </c>
-      <c r="C130" s="37">
-        <f>SUM(C120:C129)</f>
-        <v/>
-      </c>
-      <c r="D130" s="37">
-        <f>SUM(D120:D129)</f>
-        <v/>
-      </c>
-      <c r="E130" s="38">
-        <f>SUM(E120:E129)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="1" t="inlineStr">
-        <is>
-          <t>■ 除外（参考・合計には含めない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>カテゴリ</t>
-        </is>
-      </c>
-      <c r="B133" s="29" t="inlineStr">
-        <is>
-          <t>GBP 合計</t>
-        </is>
-      </c>
-      <c r="C133" s="29" t="inlineStr">
-        <is>
-          <t>EUR 合計</t>
-        </is>
-      </c>
-      <c r="D133" s="29" t="inlineStr">
-        <is>
-          <t>JPY 合計</t>
-        </is>
-      </c>
-      <c r="E133" s="29" t="inlineStr">
-        <is>
-          <t>JPY換算合計</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="30" t="inlineStr">
-        <is>
-          <t>Bills</t>
-        </is>
-      </c>
-      <c r="B134" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C134" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D134" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E134" s="32">
-        <f>B134*設定!$B$3+C134*設定!$B$4+D134</f>
-        <v/>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="30" t="inlineStr">
-        <is>
-          <t>Eating out</t>
-        </is>
-      </c>
-      <c r="B135" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C135" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D135" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E135" s="32">
-        <f>B135*設定!$B$3+C135*設定!$B$4+D135</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="30" t="inlineStr">
-        <is>
-          <t>Entertainment</t>
-        </is>
-      </c>
-      <c r="B136" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C136" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D136" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E136" s="32">
-        <f>B136*設定!$B$3+C136*設定!$B$4+D136</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="30" t="inlineStr">
-        <is>
-          <t>Family</t>
-        </is>
-      </c>
-      <c r="B137" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C137" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D137" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E137" s="32">
-        <f>B137*設定!$B$3+C137*設定!$B$4+D137</f>
-        <v/>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="30" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="B138" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C138" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D138" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E138" s="32">
-        <f>B138*設定!$B$3+C138*設定!$B$4+D138</f>
-        <v/>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="30" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="B139" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C139" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D139" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E139" s="32">
-        <f>B139*設定!$B$3+C139*設定!$B$4+D139</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="30" t="inlineStr">
-        <is>
-          <t>Money added</t>
-        </is>
-      </c>
-      <c r="B140" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C140" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D140" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E140" s="32">
-        <f>B140*設定!$B$3+C140*設定!$B$4+D140</f>
-        <v/>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="30" t="inlineStr">
-        <is>
-          <t>Personal care</t>
-        </is>
-      </c>
-      <c r="B141" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C141" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D141" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E141" s="32">
-        <f>B141*設定!$B$3+C141*設定!$B$4+D141</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="30" t="inlineStr">
-        <is>
-          <t>Shopping</t>
-        </is>
-      </c>
-      <c r="B142" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C142" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D142" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E142" s="32">
-        <f>B142*設定!$B$3+C142*設定!$B$4+D142</f>
-        <v/>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="30" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="B143" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="C143" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="D143" s="31">
-        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-08")</f>
-        <v/>
-      </c>
-      <c r="E143" s="32">
-        <f>B143*設定!$B$3+C143*設定!$B$4+D143</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="36" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="B144" s="37">
-        <f>SUM(B134:B143)</f>
-        <v/>
-      </c>
-      <c r="C144" s="37">
-        <f>SUM(C134:C143)</f>
-        <v/>
-      </c>
-      <c r="D144" s="37">
-        <f>SUM(D134:D143)</f>
-        <v/>
-      </c>
-      <c r="E144" s="38">
-        <f>SUM(E134:E143)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="51" t="inlineStr">
-        <is>
-          <t>※10月分以降のデータを追加したら、この上に同じ形式のセクションを追加します。</t>
-        </is>
-      </c>
-    </row>
+    <row r="100"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -13788,6 +12341,1473 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.8" customHeight="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>2026年9月</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>■ 聖也</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>カテゴリ</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>GBP 合計</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>EUR 合計</t>
+        </is>
+      </c>
+      <c r="D4" s="29" t="inlineStr">
+        <is>
+          <t>JPY 合計</t>
+        </is>
+      </c>
+      <c r="E4" s="29" t="inlineStr">
+        <is>
+          <t>JPY換算合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>Bills</t>
+        </is>
+      </c>
+      <c r="B5" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C5" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D5" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E5" s="32">
+        <f>B5*設定!$B$3+C5*設定!$B$4+D5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>Eating out</t>
+        </is>
+      </c>
+      <c r="B6" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C6" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D6" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E6" s="32">
+        <f>B6*設定!$B$3+C6*設定!$B$4+D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="B7" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C7" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D7" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E7" s="32">
+        <f>B7*設定!$B$3+C7*設定!$B$4+D7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="B8" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C8" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D8" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E8" s="32">
+        <f>B8*設定!$B$3+C8*設定!$B$4+D8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B9" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C9" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D9" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E9" s="32">
+        <f>B9*設定!$B$3+C9*設定!$B$4+D9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="B10" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C10" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D10" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E10" s="32">
+        <f>B10*設定!$B$3+C10*設定!$B$4+D10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="30" t="inlineStr">
+        <is>
+          <t>Money added</t>
+        </is>
+      </c>
+      <c r="B11" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C11" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D11" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E11" s="32">
+        <f>B11*設定!$B$3+C11*設定!$B$4+D11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>Personal care</t>
+        </is>
+      </c>
+      <c r="B12" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C12" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D12" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E12" s="32">
+        <f>B12*設定!$B$3+C12*設定!$B$4+D12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+      <c r="B13" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C13" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D13" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E13" s="32">
+        <f>B13*設定!$B$3+C13*設定!$B$4+D13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="B14" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C14" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D14" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"聖也",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E14" s="32">
+        <f>B14*設定!$B$3+C14*設定!$B$4+D14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="36" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B15" s="37">
+        <f>SUM(B5:B14)</f>
+        <v/>
+      </c>
+      <c r="C15" s="37">
+        <f>SUM(C5:C14)</f>
+        <v/>
+      </c>
+      <c r="D15" s="37">
+        <f>SUM(D5:D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="38">
+        <f>SUM(E5:E14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>■ 愛弓</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>カテゴリ</t>
+        </is>
+      </c>
+      <c r="B18" s="29" t="inlineStr">
+        <is>
+          <t>GBP 合計</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>EUR 合計</t>
+        </is>
+      </c>
+      <c r="D18" s="29" t="inlineStr">
+        <is>
+          <t>JPY 合計</t>
+        </is>
+      </c>
+      <c r="E18" s="29" t="inlineStr">
+        <is>
+          <t>JPY換算合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>Bills</t>
+        </is>
+      </c>
+      <c r="B19" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C19" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D19" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E19" s="32">
+        <f>B19*設定!$B$3+C19*設定!$B$4+D19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>Eating out</t>
+        </is>
+      </c>
+      <c r="B20" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C20" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D20" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E20" s="32">
+        <f>B20*設定!$B$3+C20*設定!$B$4+D20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="B21" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C21" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D21" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E21" s="32">
+        <f>B21*設定!$B$3+C21*設定!$B$4+D21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="B22" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C22" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D22" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E22" s="32">
+        <f>B22*設定!$B$3+C22*設定!$B$4+D22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B23" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C23" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D23" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E23" s="32">
+        <f>B23*設定!$B$3+C23*設定!$B$4+D23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="B24" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C24" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D24" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E24" s="32">
+        <f>B24*設定!$B$3+C24*設定!$B$4+D24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>Money added</t>
+        </is>
+      </c>
+      <c r="B25" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C25" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D25" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E25" s="32">
+        <f>B25*設定!$B$3+C25*設定!$B$4+D25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>Personal care</t>
+        </is>
+      </c>
+      <c r="B26" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C26" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D26" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E26" s="32">
+        <f>B26*設定!$B$3+C26*設定!$B$4+D26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+      <c r="B27" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C27" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D27" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E27" s="32">
+        <f>B27*設定!$B$3+C27*設定!$B$4+D27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="B28" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C28" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D28" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"愛弓",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E28" s="32">
+        <f>B28*設定!$B$3+C28*設定!$B$4+D28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="36" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B29" s="37">
+        <f>SUM(B19:B28)</f>
+        <v/>
+      </c>
+      <c r="C29" s="37">
+        <f>SUM(C19:C28)</f>
+        <v/>
+      </c>
+      <c r="D29" s="37">
+        <f>SUM(D19:D28)</f>
+        <v/>
+      </c>
+      <c r="E29" s="38">
+        <f>SUM(E19:E28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>■ 共通</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>カテゴリ</t>
+        </is>
+      </c>
+      <c r="B32" s="29" t="inlineStr">
+        <is>
+          <t>GBP 合計</t>
+        </is>
+      </c>
+      <c r="C32" s="29" t="inlineStr">
+        <is>
+          <t>EUR 合計</t>
+        </is>
+      </c>
+      <c r="D32" s="29" t="inlineStr">
+        <is>
+          <t>JPY 合計</t>
+        </is>
+      </c>
+      <c r="E32" s="29" t="inlineStr">
+        <is>
+          <t>JPY換算合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>Bills</t>
+        </is>
+      </c>
+      <c r="B33" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C33" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D33" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E33" s="32">
+        <f>B33*設定!$B$3+C33*設定!$B$4+D33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>Eating out</t>
+        </is>
+      </c>
+      <c r="B34" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C34" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D34" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E34" s="32">
+        <f>B34*設定!$B$3+C34*設定!$B$4+D34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="30" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="B35" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C35" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D35" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E35" s="32">
+        <f>B35*設定!$B$3+C35*設定!$B$4+D35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="B36" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C36" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D36" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E36" s="32">
+        <f>B36*設定!$B$3+C36*設定!$B$4+D36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B37" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C37" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D37" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E37" s="32">
+        <f>B37*設定!$B$3+C37*設定!$B$4+D37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="B38" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C38" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D38" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E38" s="32">
+        <f>B38*設定!$B$3+C38*設定!$B$4+D38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="30" t="inlineStr">
+        <is>
+          <t>Money added</t>
+        </is>
+      </c>
+      <c r="B39" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C39" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D39" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E39" s="32">
+        <f>B39*設定!$B$3+C39*設定!$B$4+D39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="30" t="inlineStr">
+        <is>
+          <t>Personal care</t>
+        </is>
+      </c>
+      <c r="B40" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C40" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D40" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E40" s="32">
+        <f>B40*設定!$B$3+C40*設定!$B$4+D40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="30" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+      <c r="B41" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C41" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D41" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E41" s="32">
+        <f>B41*設定!$B$3+C41*設定!$B$4+D41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="B42" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C42" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D42" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"共通",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E42" s="32">
+        <f>B42*設定!$B$3+C42*設定!$B$4+D42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="36" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B43" s="37">
+        <f>SUM(B33:B42)</f>
+        <v/>
+      </c>
+      <c r="C43" s="37">
+        <f>SUM(C33:C42)</f>
+        <v/>
+      </c>
+      <c r="D43" s="37">
+        <f>SUM(D33:D42)</f>
+        <v/>
+      </c>
+      <c r="E43" s="38">
+        <f>SUM(E33:E42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>■ 合計（聖也＋愛弓＋共通、除外を除く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>カテゴリ</t>
+        </is>
+      </c>
+      <c r="B46" s="29" t="inlineStr">
+        <is>
+          <t>GBP 合計</t>
+        </is>
+      </c>
+      <c r="C46" s="29" t="inlineStr">
+        <is>
+          <t>EUR 合計</t>
+        </is>
+      </c>
+      <c r="D46" s="29" t="inlineStr">
+        <is>
+          <t>JPY 合計</t>
+        </is>
+      </c>
+      <c r="E46" s="29" t="inlineStr">
+        <is>
+          <t>JPY換算合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="30" t="inlineStr">
+        <is>
+          <t>Bills</t>
+        </is>
+      </c>
+      <c r="B47" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C47" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D47" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E47" s="32">
+        <f>B47*設定!$B$3+C47*設定!$B$4+D47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="30" t="inlineStr">
+        <is>
+          <t>Eating out</t>
+        </is>
+      </c>
+      <c r="B48" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C48" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D48" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E48" s="32">
+        <f>B48*設定!$B$3+C48*設定!$B$4+D48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="30" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="B49" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C49" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D49" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E49" s="32">
+        <f>B49*設定!$B$3+C49*設定!$B$4+D49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="30" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="B50" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C50" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D50" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E50" s="32">
+        <f>B50*設定!$B$3+C50*設定!$B$4+D50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="30" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B51" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C51" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D51" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E51" s="32">
+        <f>B51*設定!$B$3+C51*設定!$B$4+D51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="30" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="B52" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C52" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D52" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E52" s="32">
+        <f>B52*設定!$B$3+C52*設定!$B$4+D52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="30" t="inlineStr">
+        <is>
+          <t>Money added</t>
+        </is>
+      </c>
+      <c r="B53" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C53" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D53" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E53" s="32">
+        <f>B53*設定!$B$3+C53*設定!$B$4+D53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="30" t="inlineStr">
+        <is>
+          <t>Personal care</t>
+        </is>
+      </c>
+      <c r="B54" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C54" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D54" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E54" s="32">
+        <f>B54*設定!$B$3+C54*設定!$B$4+D54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="30" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+      <c r="B55" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C55" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D55" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E55" s="32">
+        <f>B55*設定!$B$3+C55*設定!$B$4+D55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="30" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="B56" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C56" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D56" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"&lt;&gt;除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E56" s="32">
+        <f>B56*設定!$B$3+C56*設定!$B$4+D56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="36" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B57" s="37">
+        <f>SUM(B47:B56)</f>
+        <v/>
+      </c>
+      <c r="C57" s="37">
+        <f>SUM(C47:C56)</f>
+        <v/>
+      </c>
+      <c r="D57" s="37">
+        <f>SUM(D47:D56)</f>
+        <v/>
+      </c>
+      <c r="E57" s="38">
+        <f>SUM(E47:E56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>■ 除外（参考・合計には含めない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>カテゴリ</t>
+        </is>
+      </c>
+      <c r="B60" s="29" t="inlineStr">
+        <is>
+          <t>GBP 合計</t>
+        </is>
+      </c>
+      <c r="C60" s="29" t="inlineStr">
+        <is>
+          <t>EUR 合計</t>
+        </is>
+      </c>
+      <c r="D60" s="29" t="inlineStr">
+        <is>
+          <t>JPY 合計</t>
+        </is>
+      </c>
+      <c r="E60" s="29" t="inlineStr">
+        <is>
+          <t>JPY換算合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="30" t="inlineStr">
+        <is>
+          <t>Bills</t>
+        </is>
+      </c>
+      <c r="B61" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C61" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D61" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Bills",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E61" s="32">
+        <f>B61*設定!$B$3+C61*設定!$B$4+D61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="30" t="inlineStr">
+        <is>
+          <t>Eating out</t>
+        </is>
+      </c>
+      <c r="B62" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C62" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D62" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Eating out",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E62" s="32">
+        <f>B62*設定!$B$3+C62*設定!$B$4+D62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="30" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="B63" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C63" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D63" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Entertainment",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E63" s="32">
+        <f>B63*設定!$B$3+C63*設定!$B$4+D63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="30" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="B64" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C64" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D64" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Family",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E64" s="32">
+        <f>B64*設定!$B$3+C64*設定!$B$4+D64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="30" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B65" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C65" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D65" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"General",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E65" s="32">
+        <f>B65*設定!$B$3+C65*設定!$B$4+D65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="30" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="B66" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C66" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D66" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Groceries",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E66" s="32">
+        <f>B66*設定!$B$3+C66*設定!$B$4+D66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>Money added</t>
+        </is>
+      </c>
+      <c r="B67" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C67" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D67" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Money added",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E67" s="32">
+        <f>B67*設定!$B$3+C67*設定!$B$4+D67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Personal care</t>
+        </is>
+      </c>
+      <c r="B68" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C68" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D68" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Personal care",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E68" s="32">
+        <f>B68*設定!$B$3+C68*設定!$B$4+D68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+      <c r="B69" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C69" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D69" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Shopping",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E69" s="32">
+        <f>B69*設定!$B$3+C69*設定!$B$4+D69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="B70" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"GBP",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="C70" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"EUR",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="D70" s="31">
+        <f>SUMIFS(統合決済履歴!$C$2:$C$198,統合決済履歴!$G$2:$G$198,"Transport",統合決済履歴!$D$2:$D$198,"JPY",統合決済履歴!$F$2:$F$198,"COMPLETED",統合決済履歴!$J$2:$J$198,"除外",統合決済履歴!$K$2:$K$198,"2026-09")</f>
+        <v/>
+      </c>
+      <c r="E70" s="32">
+        <f>B70*設定!$B$3+C70*設定!$B$4+D70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="36" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B71" s="37">
+        <f>SUM(B61:B70)</f>
+        <v/>
+      </c>
+      <c r="C71" s="37">
+        <f>SUM(C61:C70)</f>
+        <v/>
+      </c>
+      <c r="D71" s="37">
+        <f>SUM(D61:D70)</f>
+        <v/>
+      </c>
+      <c r="E71" s="38">
+        <f>SUM(E61:E70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E100"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.8" customHeight="1">
       <c r="A1" s="52" t="inlineStr">
         <is>
           <t>全期間合計</t>
